--- a/output2.xlsx
+++ b/output2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10719"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2638d6317efefd9b/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/shreyanpal/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8" documentId="11_2B59D2BFD3705F75D521C3F05053483742E5E13E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{732D05AC-8D2F-47CA-A210-1AA35D54CB4C}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC125DA9-944C-E145-B2CB-93EA942BA7F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="34200" windowHeight="19900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="16">
   <si>
     <t>Lower Limit in mi/h</t>
   </si>
@@ -28,12 +28,12 @@
     <t>Upper Limit in mi/h</t>
   </si>
   <si>
+    <t>Observed Vehicles(n)</t>
+  </si>
+  <si>
     <t>Middle Speed (S) in mi/h</t>
   </si>
   <si>
-    <t>Observed Vehicles(n)</t>
-  </si>
-  <si>
     <t>% Frequency</t>
   </si>
   <si>
@@ -44,19 +44,49 @@
   </si>
   <si>
     <t>nS²</t>
+  </si>
+  <si>
+    <t>z</t>
+  </si>
+  <si>
+    <t>Probability of occurence (z≤zd)</t>
+  </si>
+  <si>
+    <t>Theoretical Frequency f</t>
+  </si>
+  <si>
+    <t>Combined Group Observed Frequency (n)</t>
+  </si>
+  <si>
+    <t>Combined Group Theoretical Frequency (f)</t>
+  </si>
+  <si>
+    <t>Chi-Square Group χ²</t>
+  </si>
+  <si>
+    <t>inf</t>
+  </si>
+  <si>
+    <t>-inf</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -67,7 +97,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -75,12 +105,30 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -383,280 +431,436 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H20"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:N20"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="16.77734375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="21" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15" customWidth="1"/>
+    <col min="2" max="2" width="19" customWidth="1"/>
+    <col min="3" max="3" width="19.83203125" customWidth="1"/>
+    <col min="4" max="4" width="22.1640625" customWidth="1"/>
+    <col min="5" max="5" width="16" customWidth="1"/>
+    <col min="6" max="6" width="22.1640625" customWidth="1"/>
+    <col min="10" max="10" width="25.1640625" customWidth="1"/>
+    <col min="11" max="11" width="23.5" customWidth="1"/>
+    <col min="12" max="12" width="35.83203125" customWidth="1"/>
+    <col min="13" max="13" width="36.83203125" customWidth="1"/>
+    <col min="14" max="14" width="16.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2">
-        <v>25</v>
-      </c>
-      <c r="B2">
-        <v>27</v>
+        <v>61</v>
+      </c>
+      <c r="B2" t="s">
+        <v>14</v>
       </c>
       <c r="C2">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="D2">
-        <v>4</v>
+        <v>62</v>
       </c>
       <c r="E2">
         <v>0.92378752886836024</v>
       </c>
       <c r="F2">
-        <v>0.92378752886836024</v>
+        <v>100</v>
       </c>
       <c r="G2">
-        <v>104</v>
+        <v>248</v>
       </c>
       <c r="H2">
-        <v>2704</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+        <v>15376</v>
+      </c>
+      <c r="I2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J2">
+        <v>5.3347073983357474E-3</v>
+      </c>
+      <c r="K2">
+        <v>2.3099283034793792</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A3">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="B3">
-        <v>29</v>
+        <v>61</v>
       </c>
       <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3">
+        <v>60</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <v>99.07621247113164</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <v>2.5533437178863299</v>
+      </c>
+      <c r="J3">
+        <v>6.2415913799851452E-3</v>
+      </c>
+      <c r="K3">
+        <v>2.7026090675335679</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>57</v>
+      </c>
+      <c r="B4">
+        <v>59</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>58</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <v>99.07621247113164</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>2.2709071794153171</v>
+      </c>
+      <c r="J4">
+        <v>1.180353266930456E-2</v>
+      </c>
+      <c r="K4">
+        <v>5.1109296458088753</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>55</v>
+      </c>
+      <c r="B5">
+        <v>57</v>
+      </c>
+      <c r="C5">
+        <v>8</v>
+      </c>
+      <c r="D5">
+        <v>56</v>
+      </c>
+      <c r="E5">
+        <v>1.84757505773672</v>
+      </c>
+      <c r="F5">
+        <v>99.07621247113164</v>
+      </c>
+      <c r="G5">
+        <v>448</v>
+      </c>
+      <c r="H5">
+        <v>25088</v>
+      </c>
+      <c r="I5">
+        <v>1.988470640944304</v>
+      </c>
+      <c r="J5">
+        <v>2.062103374000079E-2</v>
+      </c>
+      <c r="K5">
+        <v>8.9289076094203441</v>
+      </c>
+      <c r="L5">
+        <v>12</v>
+      </c>
+      <c r="M5">
+        <v>19.05237462624217</v>
+      </c>
+      <c r="N5">
+        <v>2.6104876082144362</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>53</v>
+      </c>
+      <c r="B6">
+        <v>55</v>
+      </c>
+      <c r="C6">
         <v>28</v>
       </c>
-      <c r="D3">
-        <v>4</v>
-      </c>
-      <c r="E3">
-        <v>0.92378752886836024</v>
-      </c>
-      <c r="F3">
-        <v>1.84757505773672</v>
-      </c>
-      <c r="G3">
-        <v>112</v>
-      </c>
-      <c r="H3">
-        <v>3136</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A4">
-        <v>29</v>
-      </c>
-      <c r="B4">
-        <v>31</v>
-      </c>
-      <c r="C4">
-        <v>30</v>
-      </c>
-      <c r="D4">
-        <v>6</v>
-      </c>
-      <c r="E4">
-        <v>1.38568129330254</v>
-      </c>
-      <c r="F4">
-        <v>3.2332563510392611</v>
-      </c>
-      <c r="G4">
-        <v>180</v>
-      </c>
-      <c r="H4">
-        <v>5400</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5">
-        <v>31</v>
-      </c>
-      <c r="B5">
-        <v>33</v>
-      </c>
-      <c r="C5">
-        <v>32</v>
-      </c>
-      <c r="D5">
-        <v>6</v>
-      </c>
-      <c r="E5">
-        <v>1.38568129330254</v>
-      </c>
-      <c r="F5">
-        <v>4.6189376443418011</v>
-      </c>
-      <c r="G5">
-        <v>192</v>
-      </c>
-      <c r="H5">
-        <v>6144</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6">
-        <v>33</v>
-      </c>
-      <c r="B6">
-        <v>35</v>
-      </c>
-      <c r="C6">
-        <v>34</v>
-      </c>
       <c r="D6">
+        <v>54</v>
+      </c>
+      <c r="E6">
+        <v>6.4665127020785222</v>
+      </c>
+      <c r="F6">
+        <v>97.228637413394907</v>
+      </c>
+      <c r="G6">
+        <v>1512</v>
+      </c>
+      <c r="H6">
+        <v>81648</v>
+      </c>
+      <c r="I6">
+        <v>1.706034102473291</v>
+      </c>
+      <c r="J6">
+        <v>3.328063552595184E-2</v>
+      </c>
+      <c r="K6">
+        <v>14.41051518273715</v>
+      </c>
+      <c r="L6">
+        <v>28</v>
+      </c>
+      <c r="M6">
+        <v>14.41051518273715</v>
+      </c>
+      <c r="N6">
+        <v>12.815232159072639</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>51</v>
+      </c>
+      <c r="B7">
+        <v>53</v>
+      </c>
+      <c r="C7">
+        <v>39</v>
+      </c>
+      <c r="D7">
+        <v>52</v>
+      </c>
+      <c r="E7">
+        <v>9.006928406466514</v>
+      </c>
+      <c r="F7">
+        <v>90.762124711316389</v>
+      </c>
+      <c r="G7">
+        <v>2028</v>
+      </c>
+      <c r="H7">
+        <v>105456</v>
+      </c>
+      <c r="I7">
+        <v>1.423597564002278</v>
+      </c>
+      <c r="J7">
+        <v>4.9619959223337513E-2</v>
+      </c>
+      <c r="K7">
+        <v>21.485442343705142</v>
+      </c>
+      <c r="L7">
+        <v>39</v>
+      </c>
+      <c r="M7">
+        <v>21.485442343705142</v>
+      </c>
+      <c r="N7">
+        <v>14.27756175499696</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>49</v>
+      </c>
+      <c r="B8">
+        <v>51</v>
+      </c>
+      <c r="C8">
+        <v>15</v>
+      </c>
+      <c r="D8">
+        <v>50</v>
+      </c>
+      <c r="E8">
+        <v>3.464203233256351</v>
+      </c>
+      <c r="F8">
+        <v>81.755196304849875</v>
+      </c>
+      <c r="G8">
+        <v>750</v>
+      </c>
+      <c r="H8">
+        <v>37500</v>
+      </c>
+      <c r="I8">
+        <v>1.1411610255312641</v>
+      </c>
+      <c r="J8">
+        <v>6.8344808748058039E-2</v>
+      </c>
+      <c r="K8">
+        <v>29.593302187909131</v>
+      </c>
+      <c r="L8">
+        <v>15</v>
+      </c>
+      <c r="M8">
+        <v>29.593302187909131</v>
+      </c>
+      <c r="N8">
+        <v>7.1963739428391289</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A9">
         <v>47</v>
       </c>
-      <c r="E6">
-        <v>10.85450346420323</v>
-      </c>
-      <c r="F6">
-        <v>15.473441108545041</v>
-      </c>
-      <c r="G6">
-        <v>1598</v>
-      </c>
-      <c r="H6">
-        <v>54332</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A7">
-        <v>35</v>
-      </c>
-      <c r="B7">
-        <v>37</v>
-      </c>
-      <c r="C7">
-        <v>36</v>
-      </c>
-      <c r="D7">
-        <v>27</v>
-      </c>
-      <c r="E7">
-        <v>6.2355658198614323</v>
-      </c>
-      <c r="F7">
-        <v>21.70900692840647</v>
-      </c>
-      <c r="G7">
-        <v>972</v>
-      </c>
-      <c r="H7">
-        <v>34992</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A8">
-        <v>37</v>
-      </c>
-      <c r="B8">
-        <v>39</v>
-      </c>
-      <c r="C8">
-        <v>38</v>
-      </c>
-      <c r="D8">
-        <v>38</v>
-      </c>
-      <c r="E8">
-        <v>8.7759815242494223</v>
-      </c>
-      <c r="F8">
-        <v>30.484988452655891</v>
-      </c>
-      <c r="G8">
-        <v>1444</v>
-      </c>
-      <c r="H8">
-        <v>54872</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A9">
-        <v>39</v>
-      </c>
       <c r="B9">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="C9">
         <v>40</v>
       </c>
       <c r="D9">
+        <v>48</v>
+      </c>
+      <c r="E9">
+        <v>9.2378752886836022</v>
+      </c>
+      <c r="F9">
+        <v>78.290993071593519</v>
+      </c>
+      <c r="G9">
+        <v>1920</v>
+      </c>
+      <c r="H9">
+        <v>92160</v>
+      </c>
+      <c r="I9">
+        <v>0.85872448706025106</v>
+      </c>
+      <c r="J9">
+        <v>8.6964014960698277E-2</v>
+      </c>
+      <c r="K9">
+        <v>37.655418477982352</v>
+      </c>
+      <c r="L9">
+        <v>40</v>
+      </c>
+      <c r="M9">
+        <v>37.655418477982352</v>
+      </c>
+      <c r="N9">
+        <v>0.14598330693365691</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A10">
         <v>45</v>
       </c>
-      <c r="E9">
-        <v>10.39260969976905</v>
-      </c>
-      <c r="F9">
-        <v>40.877598152424937</v>
-      </c>
-      <c r="G9">
-        <v>1800</v>
-      </c>
-      <c r="H9">
-        <v>72000</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A10">
-        <v>41</v>
-      </c>
       <c r="B10">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="C10">
-        <v>42</v>
+        <v>23</v>
       </c>
       <c r="D10">
-        <v>69</v>
+        <v>46</v>
       </c>
       <c r="E10">
-        <v>15.935334872979221</v>
+        <v>5.3117782909930717</v>
       </c>
       <c r="F10">
-        <v>56.812933025404149</v>
+        <v>69.053117782909922</v>
       </c>
       <c r="G10">
-        <v>2898</v>
+        <v>1058</v>
       </c>
       <c r="H10">
-        <v>121716</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+        <v>48668</v>
+      </c>
+      <c r="I10">
+        <v>0.57628794858923782</v>
+      </c>
+      <c r="J10">
+        <v>0.102225440727053</v>
+      </c>
+      <c r="K10">
+        <v>44.26361583481394</v>
+      </c>
+      <c r="L10">
+        <v>23</v>
+      </c>
+      <c r="M10">
+        <v>44.26361583481394</v>
+      </c>
+      <c r="N10">
+        <v>10.21474070391996</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>43</v>
       </c>
@@ -664,10 +868,10 @@
         <v>45</v>
       </c>
       <c r="C11">
+        <v>30</v>
+      </c>
+      <c r="D11">
         <v>44</v>
-      </c>
-      <c r="D11">
-        <v>30</v>
       </c>
       <c r="E11">
         <v>6.9284064665127012</v>
@@ -681,239 +885,410 @@
       <c r="H11">
         <v>58080</v>
       </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I11">
+        <v>0.29385141011822458</v>
+      </c>
+      <c r="J11">
+        <v>0.1110104995943626</v>
+      </c>
+      <c r="K11">
+        <v>48.067546324359007</v>
+      </c>
+      <c r="L11">
+        <v>30</v>
+      </c>
+      <c r="M11">
+        <v>48.067546324359007</v>
+      </c>
+      <c r="N11">
+        <v>6.7911981189984676</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A12">
+        <v>41</v>
+      </c>
+      <c r="B12">
+        <v>43</v>
+      </c>
+      <c r="C12">
+        <v>69</v>
+      </c>
+      <c r="D12">
+        <v>42</v>
+      </c>
+      <c r="E12">
+        <v>15.935334872979221</v>
+      </c>
+      <c r="F12">
+        <v>56.812933025404149</v>
+      </c>
+      <c r="G12">
+        <v>2898</v>
+      </c>
+      <c r="H12">
+        <v>121716</v>
+      </c>
+      <c r="I12">
+        <v>1.141487164721139E-2</v>
+      </c>
+      <c r="J12">
+        <v>0.111366592042855</v>
+      </c>
+      <c r="K12">
+        <v>48.221734354556233</v>
+      </c>
+      <c r="L12">
+        <v>69</v>
+      </c>
+      <c r="M12">
+        <v>48.221734354556233</v>
+      </c>
+      <c r="N12">
+        <v>8.9531479738624551</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A13">
+        <v>39</v>
+      </c>
+      <c r="B13">
+        <v>41</v>
+      </c>
+      <c r="C13">
         <v>45</v>
-      </c>
-      <c r="B12">
-        <v>47</v>
-      </c>
-      <c r="C12">
-        <v>46</v>
-      </c>
-      <c r="D12">
-        <v>23</v>
-      </c>
-      <c r="E12">
-        <v>5.3117782909930717</v>
-      </c>
-      <c r="F12">
-        <v>69.053117782909922</v>
-      </c>
-      <c r="G12">
-        <v>1058</v>
-      </c>
-      <c r="H12">
-        <v>48668</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A13">
-        <v>47</v>
-      </c>
-      <c r="B13">
-        <v>49</v>
-      </c>
-      <c r="C13">
-        <v>48</v>
       </c>
       <c r="D13">
         <v>40</v>
       </c>
       <c r="E13">
-        <v>9.2378752886836022</v>
+        <v>10.39260969976905</v>
       </c>
       <c r="F13">
-        <v>78.290993071593519</v>
+        <v>40.877598152424937</v>
       </c>
       <c r="G13">
-        <v>1920</v>
+        <v>1800</v>
       </c>
       <c r="H13">
-        <v>92160</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+        <v>72000</v>
+      </c>
+      <c r="I13">
+        <v>-0.27102166682380191</v>
+      </c>
+      <c r="J13">
+        <v>0.1032123379458266</v>
+      </c>
+      <c r="K13">
+        <v>44.690942330542931</v>
+      </c>
+      <c r="L13">
+        <v>45</v>
+      </c>
+      <c r="M13">
+        <v>44.690942330542931</v>
+      </c>
+      <c r="N13">
+        <v>2.137270732484783E-3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A14">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="B14">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="C14">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="D14">
+        <v>38</v>
+      </c>
+      <c r="E14">
+        <v>8.7759815242494223</v>
+      </c>
+      <c r="F14">
+        <v>30.484988452655891</v>
+      </c>
+      <c r="G14">
+        <v>1444</v>
+      </c>
+      <c r="H14">
+        <v>54872</v>
+      </c>
+      <c r="I14">
+        <v>-0.55345820529481504</v>
+      </c>
+      <c r="J14">
+        <v>8.8367786203170928E-2</v>
+      </c>
+      <c r="K14">
+        <v>38.26325142597301</v>
+      </c>
+      <c r="L14">
+        <v>38</v>
+      </c>
+      <c r="M14">
+        <v>38.26325142597301</v>
+      </c>
+      <c r="N14">
+        <v>1.8111715730927569E-3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A15">
+        <v>35</v>
+      </c>
+      <c r="B15">
+        <v>37</v>
+      </c>
+      <c r="C15">
+        <v>27</v>
+      </c>
+      <c r="D15">
+        <v>36</v>
+      </c>
+      <c r="E15">
+        <v>6.2355658198614323</v>
+      </c>
+      <c r="F15">
+        <v>21.70900692840647</v>
+      </c>
+      <c r="G15">
+        <v>972</v>
+      </c>
+      <c r="H15">
+        <v>34992</v>
+      </c>
+      <c r="I15">
+        <v>-0.83589474376582829</v>
+      </c>
+      <c r="J15">
+        <v>6.9894294229301213E-2</v>
+      </c>
+      <c r="K15">
+        <v>30.26422940128743</v>
+      </c>
+      <c r="L15">
+        <v>27</v>
+      </c>
+      <c r="M15">
+        <v>30.26422940128743</v>
+      </c>
+      <c r="N15">
+        <v>0.35207219199098472</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A16">
+        <v>33</v>
+      </c>
+      <c r="B16">
+        <v>35</v>
+      </c>
+      <c r="C16">
+        <v>47</v>
+      </c>
+      <c r="D16">
+        <v>34</v>
+      </c>
+      <c r="E16">
+        <v>10.85450346420323</v>
+      </c>
+      <c r="F16">
+        <v>15.473441108545041</v>
+      </c>
+      <c r="G16">
+        <v>1598</v>
+      </c>
+      <c r="H16">
+        <v>54332</v>
+      </c>
+      <c r="I16">
+        <v>-1.118331282236841</v>
+      </c>
+      <c r="J16">
+        <v>5.1071008447348243E-2</v>
+      </c>
+      <c r="K16">
+        <v>22.113746657701789</v>
+      </c>
+      <c r="L16">
+        <v>47</v>
+      </c>
+      <c r="M16">
+        <v>22.113746657701789</v>
+      </c>
+      <c r="N16">
+        <v>28.006362513036649</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A17">
+        <v>31</v>
+      </c>
+      <c r="B17">
+        <v>33</v>
+      </c>
+      <c r="C17">
+        <v>6</v>
+      </c>
+      <c r="D17">
+        <v>32</v>
+      </c>
+      <c r="E17">
+        <v>1.38568129330254</v>
+      </c>
+      <c r="F17">
+        <v>4.6189376443418011</v>
+      </c>
+      <c r="G17">
+        <v>192</v>
+      </c>
+      <c r="H17">
+        <v>6144</v>
+      </c>
+      <c r="I17">
+        <v>-1.4007678207078551</v>
+      </c>
+      <c r="J17">
+        <v>3.44739885411511E-2</v>
+      </c>
+      <c r="K17">
+        <v>14.927237038318429</v>
+      </c>
+      <c r="L17">
+        <v>6</v>
+      </c>
+      <c r="M17">
+        <v>14.927237038318429</v>
+      </c>
+      <c r="N17">
+        <v>5.3389358615894356</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A18">
+        <v>29</v>
+      </c>
+      <c r="B18">
+        <v>31</v>
+      </c>
+      <c r="C18">
+        <v>6</v>
+      </c>
+      <c r="D18">
+        <v>30</v>
+      </c>
+      <c r="E18">
+        <v>1.38568129330254</v>
+      </c>
+      <c r="F18">
+        <v>3.2332563510392611</v>
+      </c>
+      <c r="G18">
+        <v>180</v>
+      </c>
+      <c r="H18">
+        <v>5400</v>
+      </c>
+      <c r="I18">
+        <v>-1.6832043591788679</v>
+      </c>
+      <c r="J18">
+        <v>2.1497715441057049E-2</v>
+      </c>
+      <c r="K18">
+        <v>9.3085107859777025</v>
+      </c>
+      <c r="L18">
+        <v>6</v>
+      </c>
+      <c r="M18">
+        <v>9.3085107859777025</v>
+      </c>
+      <c r="N18">
+        <v>1.175939296049392</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A19">
+        <v>27</v>
+      </c>
+      <c r="B19">
+        <v>29</v>
+      </c>
+      <c r="C19">
+        <v>4</v>
+      </c>
+      <c r="D19">
+        <v>28</v>
+      </c>
+      <c r="E19">
+        <v>0.92378752886836024</v>
+      </c>
+      <c r="F19">
+        <v>1.84757505773672</v>
+      </c>
+      <c r="G19">
+        <v>112</v>
+      </c>
+      <c r="H19">
+        <v>3136</v>
+      </c>
+      <c r="I19">
+        <v>-1.9656408976498809</v>
+      </c>
+      <c r="J19">
+        <v>1.238442688373655E-2</v>
+      </c>
+      <c r="K19">
+        <v>5.3624568406579272</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
         <v>15</v>
       </c>
-      <c r="E14">
-        <v>3.464203233256351</v>
-      </c>
-      <c r="F14">
-        <v>81.755196304849875</v>
-      </c>
-      <c r="G14">
-        <v>750</v>
-      </c>
-      <c r="H14">
-        <v>37500</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A15">
-        <v>51</v>
-      </c>
-      <c r="B15">
-        <v>53</v>
-      </c>
-      <c r="C15">
-        <v>52</v>
-      </c>
-      <c r="D15">
-        <v>39</v>
-      </c>
-      <c r="E15">
-        <v>9.006928406466514</v>
-      </c>
-      <c r="F15">
-        <v>90.762124711316389</v>
-      </c>
-      <c r="G15">
-        <v>2028</v>
-      </c>
-      <c r="H15">
-        <v>105456</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A16">
-        <v>53</v>
-      </c>
-      <c r="B16">
-        <v>55</v>
-      </c>
-      <c r="C16">
-        <v>54</v>
-      </c>
-      <c r="D16">
-        <v>28</v>
-      </c>
-      <c r="E16">
-        <v>6.4665127020785222</v>
-      </c>
-      <c r="F16">
-        <v>97.228637413394907</v>
-      </c>
-      <c r="G16">
-        <v>1512</v>
-      </c>
-      <c r="H16">
-        <v>81648</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A17">
-        <v>55</v>
-      </c>
-      <c r="B17">
-        <v>57</v>
-      </c>
-      <c r="C17">
-        <v>56</v>
-      </c>
-      <c r="D17">
-        <v>8</v>
-      </c>
-      <c r="E17">
-        <v>1.84757505773672</v>
-      </c>
-      <c r="F17">
-        <v>99.07621247113164</v>
-      </c>
-      <c r="G17">
-        <v>448</v>
-      </c>
-      <c r="H17">
-        <v>25088</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A18">
-        <v>57</v>
-      </c>
-      <c r="B18">
-        <v>59</v>
-      </c>
-      <c r="C18">
-        <v>58</v>
-      </c>
-      <c r="D18">
-        <v>0</v>
-      </c>
-      <c r="E18">
-        <v>0</v>
-      </c>
-      <c r="F18">
-        <v>99.07621247113164</v>
-      </c>
-      <c r="G18">
-        <v>0</v>
-      </c>
-      <c r="H18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A19">
-        <v>59</v>
-      </c>
-      <c r="B19">
-        <v>61</v>
-      </c>
-      <c r="C19">
-        <v>60</v>
-      </c>
-      <c r="D19">
-        <v>0</v>
-      </c>
-      <c r="E19">
-        <v>0</v>
-      </c>
-      <c r="F19">
-        <v>99.07621247113164</v>
-      </c>
-      <c r="G19">
-        <v>0</v>
-      </c>
-      <c r="H19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A20">
-        <v>61</v>
-      </c>
       <c r="B20">
-        <v>63</v>
+        <v>27</v>
       </c>
       <c r="C20">
-        <v>62</v>
+        <v>4</v>
       </c>
       <c r="D20">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="E20">
         <v>0.92378752886836024</v>
       </c>
       <c r="F20">
-        <v>100</v>
+        <v>0.92378752886836024</v>
       </c>
       <c r="G20">
-        <v>248</v>
+        <v>104</v>
       </c>
       <c r="H20">
-        <v>15376</v>
+        <v>2704</v>
+      </c>
+      <c r="I20">
+        <v>-2.2480774361208939</v>
+      </c>
+      <c r="J20">
+        <v>1.228562629846577E-2</v>
+      </c>
+      <c r="K20">
+        <v>5.3196761872356761</v>
+      </c>
+      <c r="L20">
+        <v>8</v>
+      </c>
+      <c r="M20">
+        <v>10.682133027893601</v>
+      </c>
+      <c r="N20">
+        <v>0.67344579594102361</v>
       </c>
     </row>
   </sheetData>
